--- a/output/2026-10-06/enriched_analysis.xlsx
+++ b/output/2026-10-06/enriched_analysis.xlsx
@@ -1161,10 +1161,10 @@
         </is>
       </c>
       <c r="V3" t="n">
-        <v>2.2</v>
+        <v>2.201</v>
       </c>
       <c r="W3" t="n">
-        <v>2864</v>
+        <v>2863</v>
       </c>
       <c r="X3" t="n">
         <v>22.4</v>
@@ -1393,13 +1393,13 @@
         </is>
       </c>
       <c r="V4" t="n">
-        <v>1.155</v>
+        <v>1.159</v>
       </c>
       <c r="W4" t="n">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="X4" t="n">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="Y4" t="n">
         <v>22</v>
@@ -2093,7 +2093,7 @@
         <v>922</v>
       </c>
       <c r="X7" t="n">
-        <v>9.06</v>
+        <v>9.07</v>
       </c>
       <c r="Y7" t="n">
         <v>7</v>
@@ -2319,10 +2319,10 @@
         </is>
       </c>
       <c r="V8" t="n">
-        <v>0.533</v>
+        <v>0.532</v>
       </c>
       <c r="W8" t="n">
-        <v>2681</v>
+        <v>2682</v>
       </c>
       <c r="X8" t="n">
         <v>22</v>
@@ -2551,13 +2551,13 @@
         </is>
       </c>
       <c r="V9" t="n">
-        <v>1.091</v>
+        <v>1.062</v>
       </c>
       <c r="W9" t="n">
-        <v>184</v>
+        <v>189</v>
       </c>
       <c r="X9" t="n">
-        <v>7.83</v>
+        <v>8.01</v>
       </c>
       <c r="Y9" t="n">
         <v>17</v>
@@ -2786,10 +2786,10 @@
         <v>0.049</v>
       </c>
       <c r="W10" t="n">
-        <v>14738</v>
+        <v>14755</v>
       </c>
       <c r="X10" t="n">
-        <v>37.5</v>
+        <v>37.6</v>
       </c>
       <c r="Y10" t="n">
         <v>83</v>
@@ -3018,7 +3018,7 @@
         <v>0.128</v>
       </c>
       <c r="W11" t="n">
-        <v>2447</v>
+        <v>2446</v>
       </c>
       <c r="X11" t="n">
         <v>21.4</v>
@@ -3247,13 +3247,13 @@
         </is>
       </c>
       <c r="V12" t="n">
-        <v>2.305</v>
+        <v>2.316</v>
       </c>
       <c r="W12" t="n">
-        <v>2547</v>
+        <v>2534</v>
       </c>
       <c r="X12" t="n">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="Y12" t="n">
         <v>6</v>
@@ -3479,13 +3479,13 @@
         </is>
       </c>
       <c r="V13" t="n">
-        <v>2.783</v>
+        <v>2.787</v>
       </c>
       <c r="W13" t="n">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="X13" t="n">
-        <v>26.6</v>
+        <v>26.5</v>
       </c>
       <c r="Y13" t="n">
         <v>30</v>
@@ -3705,13 +3705,13 @@
         </is>
       </c>
       <c r="V14" t="n">
-        <v>0.067</v>
+        <v>0.066</v>
       </c>
       <c r="W14" t="n">
-        <v>838</v>
+        <v>858</v>
       </c>
       <c r="X14" t="n">
-        <v>21.2</v>
+        <v>21.7</v>
       </c>
       <c r="Y14" t="n">
         <v>19</v>
@@ -3938,7 +3938,7 @@
         <v>0.052</v>
       </c>
       <c r="W15" t="n">
-        <v>1588</v>
+        <v>1591</v>
       </c>
       <c r="X15" t="n">
         <v>21.4</v>
@@ -4170,10 +4170,10 @@
         <v>0.064</v>
       </c>
       <c r="W16" t="n">
-        <v>1732</v>
+        <v>1742</v>
       </c>
       <c r="X16" t="n">
-        <v>39.8</v>
+        <v>40</v>
       </c>
       <c r="Y16" t="n">
         <v>20</v>
@@ -4402,10 +4402,10 @@
         <v>0.129</v>
       </c>
       <c r="W17" t="n">
-        <v>666</v>
+        <v>668</v>
       </c>
       <c r="X17" t="n">
-        <v>29</v>
+        <v>29.1</v>
       </c>
       <c r="Y17" t="n">
         <v>17</v>
@@ -4628,7 +4628,7 @@
         <v>0.008999999999999999</v>
       </c>
       <c r="W18" t="n">
-        <v>53461</v>
+        <v>53450</v>
       </c>
       <c r="X18" t="n">
         <v>45.3</v>
@@ -4857,13 +4857,13 @@
         </is>
       </c>
       <c r="V19" t="n">
-        <v>0.199</v>
+        <v>0.192</v>
       </c>
       <c r="W19" t="n">
-        <v>556</v>
+        <v>578</v>
       </c>
       <c r="X19" t="n">
-        <v>46.5</v>
+        <v>48.3</v>
       </c>
       <c r="Y19" t="n">
         <v>3</v>
@@ -5089,10 +5089,10 @@
         </is>
       </c>
       <c r="V20" t="n">
-        <v>0.089</v>
+        <v>0.09</v>
       </c>
       <c r="W20" t="n">
-        <v>638</v>
+        <v>635</v>
       </c>
       <c r="X20" t="n">
         <v>10.4</v>
@@ -5324,7 +5324,7 @@
         <v>0.375</v>
       </c>
       <c r="W21" t="n">
-        <v>1049</v>
+        <v>1048</v>
       </c>
       <c r="X21" t="n">
         <v>53.4</v>
@@ -5553,10 +5553,10 @@
         </is>
       </c>
       <c r="V22" t="n">
-        <v>0.67</v>
+        <v>0.668</v>
       </c>
       <c r="W22" t="n">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="X22" t="n">
         <v>10.8</v>
@@ -5785,13 +5785,13 @@
         </is>
       </c>
       <c r="V23" t="n">
-        <v>0.517</v>
+        <v>0.513</v>
       </c>
       <c r="W23" t="n">
-        <v>386</v>
+        <v>389</v>
       </c>
       <c r="X23" t="n">
-        <v>35.8</v>
+        <v>36.1</v>
       </c>
       <c r="Y23" t="n">
         <v>21</v>
@@ -6017,13 +6017,13 @@
         </is>
       </c>
       <c r="V24" t="n">
-        <v>0.332</v>
+        <v>0.334</v>
       </c>
       <c r="W24" t="n">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="X24" t="n">
-        <v>23.1</v>
+        <v>22.9</v>
       </c>
       <c r="Y24" t="n">
         <v>12</v>
@@ -6249,13 +6249,13 @@
         </is>
       </c>
       <c r="V25" t="n">
-        <v>0.287</v>
+        <v>0.286</v>
       </c>
       <c r="W25" t="n">
-        <v>908</v>
+        <v>910</v>
       </c>
       <c r="X25" t="n">
-        <v>24.7</v>
+        <v>24.8</v>
       </c>
       <c r="Y25" t="n">
         <v>9</v>
@@ -6481,13 +6481,13 @@
         </is>
       </c>
       <c r="V26" t="n">
-        <v>0.982</v>
+        <v>0.977</v>
       </c>
       <c r="W26" t="n">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="X26" t="n">
-        <v>5.91</v>
+        <v>5.93</v>
       </c>
       <c r="Y26" t="n">
         <v>31</v>
@@ -7171,10 +7171,10 @@
         </is>
       </c>
       <c r="V29" t="n">
-        <v>0.135</v>
+        <v>0.134</v>
       </c>
       <c r="W29" t="n">
-        <v>594</v>
+        <v>596</v>
       </c>
       <c r="X29" t="n">
         <v>13.1</v>
@@ -7406,10 +7406,10 @@
         <v>0.044</v>
       </c>
       <c r="W30" t="n">
-        <v>1591</v>
+        <v>1586</v>
       </c>
       <c r="X30" t="n">
-        <v>20.8</v>
+        <v>20.7</v>
       </c>
       <c r="Y30" t="n">
         <v>10</v>
@@ -7867,13 +7867,13 @@
         </is>
       </c>
       <c r="V32" t="n">
-        <v>0.234</v>
+        <v>0.233</v>
       </c>
       <c r="W32" t="n">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="X32" t="n">
-        <v>14.6</v>
+        <v>14.7</v>
       </c>
       <c r="Y32" t="n">
         <v>16</v>
@@ -8099,13 +8099,13 @@
         </is>
       </c>
       <c r="V33" t="n">
-        <v>0.677</v>
+        <v>0.667</v>
       </c>
       <c r="W33" t="n">
-        <v>347</v>
+        <v>352</v>
       </c>
       <c r="X33" t="n">
-        <v>1120</v>
+        <v>1137</v>
       </c>
       <c r="Y33" t="n">
         <v>-61</v>
@@ -8327,13 +8327,13 @@
         </is>
       </c>
       <c r="V34" t="n">
-        <v>0.373</v>
+        <v>0.374</v>
       </c>
       <c r="W34" t="n">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="X34" t="n">
-        <v>92.7</v>
+        <v>92.59999999999999</v>
       </c>
       <c r="Y34" t="n">
         <v>246</v>
@@ -8788,10 +8788,10 @@
         <v>0.233</v>
       </c>
       <c r="W36" t="n">
-        <v>1716</v>
+        <v>1715</v>
       </c>
       <c r="X36" t="n">
-        <v>18.2</v>
+        <v>18.1</v>
       </c>
       <c r="Y36" t="n">
         <v>-3</v>
@@ -9020,7 +9020,7 @@
         <v>0.042</v>
       </c>
       <c r="W37" t="n">
-        <v>3168</v>
+        <v>3170</v>
       </c>
       <c r="X37" t="n">
         <v>18.8</v>
@@ -9252,7 +9252,7 @@
         <v>0.011</v>
       </c>
       <c r="W38" t="n">
-        <v>4209</v>
+        <v>4185</v>
       </c>
       <c r="X38" t="inlineStr"/>
       <c r="Y38" t="n">
@@ -9482,7 +9482,7 @@
         <v>0</v>
       </c>
       <c r="W39" t="n">
-        <v>4988</v>
+        <v>4986</v>
       </c>
       <c r="X39" t="n">
         <v>11.7</v>
@@ -9714,10 +9714,10 @@
         <v>0.109</v>
       </c>
       <c r="W40" t="n">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="X40" t="n">
-        <v>7.33</v>
+        <v>7.37</v>
       </c>
       <c r="Y40" t="n">
         <v>118</v>
@@ -9942,10 +9942,10 @@
         <v>0.078</v>
       </c>
       <c r="W41" t="n">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="X41" t="n">
-        <v>12.7</v>
+        <v>12.8</v>
       </c>
       <c r="Y41" t="n">
         <v>-8</v>
@@ -10403,10 +10403,10 @@
         </is>
       </c>
       <c r="V43" t="n">
-        <v>0.052</v>
+        <v>0.053</v>
       </c>
       <c r="W43" t="n">
-        <v>943</v>
+        <v>937</v>
       </c>
       <c r="X43" t="inlineStr"/>
       <c r="Y43" t="n">
@@ -10868,7 +10868,7 @@
         <v>0.006</v>
       </c>
       <c r="W45" t="n">
-        <v>4853</v>
+        <v>4858</v>
       </c>
       <c r="X45" t="n">
         <v>12.5</v>
@@ -11096,10 +11096,10 @@
         <v>0</v>
       </c>
       <c r="W46" t="n">
-        <v>3844</v>
+        <v>3825</v>
       </c>
       <c r="X46" t="n">
-        <v>86.5</v>
+        <v>86.09999999999999</v>
       </c>
       <c r="Y46" t="n">
         <v>42</v>
@@ -11325,13 +11325,13 @@
         </is>
       </c>
       <c r="V47" t="n">
-        <v>0.218</v>
+        <v>0.217</v>
       </c>
       <c r="W47" t="n">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="X47" t="n">
-        <v>24.5</v>
+        <v>24.6</v>
       </c>
       <c r="Y47" t="n">
         <v>21</v>
@@ -11560,10 +11560,10 @@
         <v>0</v>
       </c>
       <c r="W48" t="n">
-        <v>112087</v>
+        <v>111934</v>
       </c>
       <c r="X48" t="n">
-        <v>32.3</v>
+        <v>32.2</v>
       </c>
       <c r="Y48" t="n">
         <v>18</v>

--- a/output/2026-10-06/enriched_analysis.xlsx
+++ b/output/2026-10-06/enriched_analysis.xlsx
@@ -929,13 +929,13 @@
         </is>
       </c>
       <c r="V2" t="n">
-        <v>0.857</v>
+        <v>0.847</v>
       </c>
       <c r="W2" t="n">
-        <v>945</v>
+        <v>956</v>
       </c>
       <c r="X2" t="n">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="Y2" t="n">
         <v>47</v>
@@ -1161,13 +1161,13 @@
         </is>
       </c>
       <c r="V3" t="n">
-        <v>2.201</v>
+        <v>2.203</v>
       </c>
       <c r="W3" t="n">
-        <v>2863</v>
+        <v>2860</v>
       </c>
       <c r="X3" t="n">
-        <v>22.4</v>
+        <v>22.3</v>
       </c>
       <c r="Y3" t="n">
         <v>75</v>
@@ -1393,13 +1393,13 @@
         </is>
       </c>
       <c r="V4" t="n">
-        <v>1.159</v>
+        <v>1.148</v>
       </c>
       <c r="W4" t="n">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c r="X4" t="n">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="Y4" t="n">
         <v>22</v>
@@ -1625,10 +1625,10 @@
         </is>
       </c>
       <c r="V5" t="n">
-        <v>1.622</v>
+        <v>1.696</v>
       </c>
       <c r="W5" t="n">
-        <v>320</v>
+        <v>306</v>
       </c>
       <c r="X5" t="inlineStr"/>
       <c r="Y5" t="n">
@@ -1855,13 +1855,13 @@
         </is>
       </c>
       <c r="V6" t="n">
-        <v>0.049</v>
+        <v>0.048</v>
       </c>
       <c r="W6" t="n">
-        <v>2726</v>
+        <v>2767</v>
       </c>
       <c r="X6" t="n">
-        <v>9.369999999999999</v>
+        <v>9.49</v>
       </c>
       <c r="Y6" t="n">
         <v>36</v>
@@ -2087,13 +2087,13 @@
         </is>
       </c>
       <c r="V7" t="n">
-        <v>0.332</v>
+        <v>0.327</v>
       </c>
       <c r="W7" t="n">
-        <v>922</v>
+        <v>936</v>
       </c>
       <c r="X7" t="n">
-        <v>9.07</v>
+        <v>9.18</v>
       </c>
       <c r="Y7" t="n">
         <v>7</v>
@@ -2322,7 +2322,7 @@
         <v>0.532</v>
       </c>
       <c r="W8" t="n">
-        <v>2682</v>
+        <v>2685</v>
       </c>
       <c r="X8" t="n">
         <v>22</v>
@@ -2551,13 +2551,13 @@
         </is>
       </c>
       <c r="V9" t="n">
-        <v>1.062</v>
+        <v>1.073</v>
       </c>
       <c r="W9" t="n">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="X9" t="n">
-        <v>8.01</v>
+        <v>7.94</v>
       </c>
       <c r="Y9" t="n">
         <v>17</v>
@@ -2786,7 +2786,7 @@
         <v>0.049</v>
       </c>
       <c r="W10" t="n">
-        <v>14755</v>
+        <v>14751</v>
       </c>
       <c r="X10" t="n">
         <v>37.6</v>
@@ -3015,13 +3015,13 @@
         </is>
       </c>
       <c r="V11" t="n">
-        <v>0.128</v>
+        <v>0.127</v>
       </c>
       <c r="W11" t="n">
-        <v>2446</v>
+        <v>2468</v>
       </c>
       <c r="X11" t="n">
-        <v>21.4</v>
+        <v>21.7</v>
       </c>
       <c r="Y11" t="n">
         <v>-3</v>
@@ -3247,13 +3247,13 @@
         </is>
       </c>
       <c r="V12" t="n">
-        <v>2.316</v>
+        <v>2.293</v>
       </c>
       <c r="W12" t="n">
-        <v>2534</v>
+        <v>2560</v>
       </c>
       <c r="X12" t="n">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="Y12" t="n">
         <v>6</v>
@@ -3479,13 +3479,13 @@
         </is>
       </c>
       <c r="V13" t="n">
-        <v>2.787</v>
+        <v>2.688</v>
       </c>
       <c r="W13" t="n">
-        <v>706</v>
+        <v>732</v>
       </c>
       <c r="X13" t="n">
-        <v>26.5</v>
+        <v>27.5</v>
       </c>
       <c r="Y13" t="n">
         <v>30</v>
@@ -3705,13 +3705,13 @@
         </is>
       </c>
       <c r="V14" t="n">
-        <v>0.066</v>
+        <v>0.065</v>
       </c>
       <c r="W14" t="n">
-        <v>858</v>
+        <v>873</v>
       </c>
       <c r="X14" t="n">
-        <v>21.7</v>
+        <v>22.1</v>
       </c>
       <c r="Y14" t="n">
         <v>19</v>
@@ -3935,13 +3935,13 @@
         </is>
       </c>
       <c r="V15" t="n">
-        <v>0.052</v>
+        <v>0.048</v>
       </c>
       <c r="W15" t="n">
-        <v>1591</v>
+        <v>1715</v>
       </c>
       <c r="X15" t="n">
-        <v>21.4</v>
+        <v>23</v>
       </c>
       <c r="Y15" t="n">
         <v>55</v>
@@ -4167,13 +4167,13 @@
         </is>
       </c>
       <c r="V16" t="n">
-        <v>0.064</v>
+        <v>0.063</v>
       </c>
       <c r="W16" t="n">
-        <v>1742</v>
+        <v>1753</v>
       </c>
       <c r="X16" t="n">
-        <v>40</v>
+        <v>40.2</v>
       </c>
       <c r="Y16" t="n">
         <v>20</v>
@@ -4399,13 +4399,13 @@
         </is>
       </c>
       <c r="V17" t="n">
-        <v>0.129</v>
+        <v>0.123</v>
       </c>
       <c r="W17" t="n">
-        <v>668</v>
+        <v>700</v>
       </c>
       <c r="X17" t="n">
-        <v>29.1</v>
+        <v>30.5</v>
       </c>
       <c r="Y17" t="n">
         <v>17</v>
@@ -4628,10 +4628,10 @@
         <v>0.008999999999999999</v>
       </c>
       <c r="W18" t="n">
-        <v>53450</v>
+        <v>54452</v>
       </c>
       <c r="X18" t="n">
-        <v>45.3</v>
+        <v>46.1</v>
       </c>
       <c r="Y18" t="n">
         <v>5</v>
@@ -4857,13 +4857,13 @@
         </is>
       </c>
       <c r="V19" t="n">
-        <v>0.192</v>
+        <v>0.175</v>
       </c>
       <c r="W19" t="n">
-        <v>578</v>
+        <v>632</v>
       </c>
       <c r="X19" t="n">
-        <v>48.3</v>
+        <v>52.8</v>
       </c>
       <c r="Y19" t="n">
         <v>3</v>
@@ -5089,13 +5089,13 @@
         </is>
       </c>
       <c r="V20" t="n">
-        <v>0.09</v>
+        <v>0.08699999999999999</v>
       </c>
       <c r="W20" t="n">
-        <v>635</v>
+        <v>654</v>
       </c>
       <c r="X20" t="n">
-        <v>10.4</v>
+        <v>10.6</v>
       </c>
       <c r="Y20" t="n">
         <v>-5</v>
@@ -5321,13 +5321,13 @@
         </is>
       </c>
       <c r="V21" t="n">
-        <v>0.375</v>
+        <v>0.373</v>
       </c>
       <c r="W21" t="n">
-        <v>1048</v>
+        <v>1054</v>
       </c>
       <c r="X21" t="n">
-        <v>53.4</v>
+        <v>53.7</v>
       </c>
       <c r="Y21" t="n">
         <v>21</v>
@@ -5553,13 +5553,13 @@
         </is>
       </c>
       <c r="V22" t="n">
-        <v>0.668</v>
+        <v>0.662</v>
       </c>
       <c r="W22" t="n">
-        <v>434</v>
+        <v>438</v>
       </c>
       <c r="X22" t="n">
-        <v>10.8</v>
+        <v>11</v>
       </c>
       <c r="Y22" t="n">
         <v>19</v>
@@ -5785,13 +5785,13 @@
         </is>
       </c>
       <c r="V23" t="n">
-        <v>0.513</v>
+        <v>0.516</v>
       </c>
       <c r="W23" t="n">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="X23" t="n">
-        <v>36.1</v>
+        <v>35.9</v>
       </c>
       <c r="Y23" t="n">
         <v>21</v>
@@ -5945,12 +5945,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>TAINWALCHM</t>
+          <t>SRGHFL</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>TAINWALA CHEMICALS AND PLASTICS (INDIA) LIMITED</t>
+          <t>SRG HOUSING FINANCE LIMITED</t>
         </is>
       </c>
       <c r="C24" t="n">
@@ -5962,40 +5962,40 @@
         </is>
       </c>
       <c r="E24" t="n">
+        <v>16</v>
+      </c>
+      <c r="F24" t="n">
         <v>7</v>
       </c>
-      <c r="F24" t="n">
-        <v>6</v>
-      </c>
       <c r="G24" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="I24" t="n">
-        <v>197.18</v>
+        <v>128.99</v>
       </c>
       <c r="J24" t="n">
-        <v>210.19</v>
+        <v>132.2</v>
       </c>
       <c r="K24" t="n">
-        <v>-6.2</v>
+        <v>-2.4</v>
       </c>
       <c r="L24" t="n">
-        <v>67.04000000000001</v>
+        <v>67.83</v>
       </c>
       <c r="M24" t="n">
-        <v>0.62</v>
+        <v>1.98</v>
       </c>
       <c r="N24" t="n">
-        <v>6171564</v>
+        <v>19830410</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
       </c>
       <c r="P24" t="n">
-        <v>6171564</v>
+        <v>19830410</v>
       </c>
       <c r="Q24" t="n">
         <v>0</v>
@@ -6009,60 +6009,56 @@
         <v>0</v>
       </c>
       <c r="T24" t="n">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="U24" t="inlineStr">
         <is>
-          <t>28-09-2026</t>
+          <t>16-09-2026</t>
         </is>
       </c>
       <c r="V24" t="n">
-        <v>0.334</v>
+        <v>1.027</v>
       </c>
       <c r="W24" t="n">
-        <v>185</v>
+        <v>193</v>
       </c>
       <c r="X24" t="n">
-        <v>22.9</v>
+        <v>5.66</v>
       </c>
       <c r="Y24" t="n">
-        <v>12</v>
-      </c>
-      <c r="Z24" t="n">
-        <v>0.03</v>
-      </c>
+        <v>31</v>
+      </c>
+      <c r="Z24" t="inlineStr"/>
       <c r="AA24" t="n">
-        <v>16</v>
+        <v>35</v>
       </c>
       <c r="AB24" t="n">
-        <v>0.03</v>
+        <v>5.39</v>
       </c>
       <c r="AC24" t="n">
-        <v>7.91</v>
+        <v>11.8</v>
       </c>
       <c r="AD24" t="n">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="AE24" t="b">
         <v>0</v>
       </c>
-      <c r="AF24" t="n">
-        <v>3.16</v>
-      </c>
+      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="n">
-        <v>208.99</v>
+        <v>230.38</v>
       </c>
       <c r="AH24" t="n">
-        <v>197.37</v>
+        <v>266.47</v>
       </c>
       <c r="AI24" t="n">
-        <v>10.4</v>
+        <v>-48</v>
       </c>
       <c r="AJ24" t="n">
-        <v>210.188815475785</v>
+        <v>132.2027333333333</v>
       </c>
       <c r="AK24" t="n">
-        <v>-6.2</v>
+        <v>-2.4</v>
       </c>
       <c r="AL24" t="inlineStr">
         <is>
@@ -6081,91 +6077,91 @@
       </c>
       <c r="AO24" t="inlineStr">
         <is>
-          <t>18-08-2026</t>
+          <t>15-09-2026</t>
         </is>
       </c>
       <c r="AP24" t="inlineStr">
         <is>
-          <t>28-09-2026</t>
+          <t>16-09-2026</t>
         </is>
       </c>
       <c r="AQ24" t="n">
-        <v>41</v>
+        <v>1</v>
       </c>
       <c r="AR24" t="n">
-        <v>49</v>
+        <v>21</v>
       </c>
       <c r="AS24" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="AT24" t="n">
         <v>0</v>
       </c>
       <c r="AU24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV24" t="n">
+        <v>3</v>
+      </c>
+      <c r="AW24" t="n">
+        <v>3</v>
+      </c>
+      <c r="AX24" t="n">
+        <v>3</v>
+      </c>
+      <c r="AY24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ24" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA24" t="n">
+        <v>19830410</v>
+      </c>
+      <c r="BB24" t="n">
+        <v>19830410</v>
+      </c>
+      <c r="BC24" t="n">
+        <v>19830410</v>
+      </c>
+      <c r="BD24" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE24" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF24" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG24" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH24" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI24" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ24" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK24" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL24" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM24" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN24" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO24" t="n">
+        <v>19830410</v>
+      </c>
+      <c r="BP24" t="n">
         <v>2</v>
-      </c>
-      <c r="AV24" t="n">
-        <v>8</v>
-      </c>
-      <c r="AW24" t="n">
-        <v>14</v>
-      </c>
-      <c r="AX24" t="n">
-        <v>14</v>
-      </c>
-      <c r="AY24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ24" t="n">
-        <v>226572</v>
-      </c>
-      <c r="BA24" t="n">
-        <v>3273287</v>
-      </c>
-      <c r="BB24" t="n">
-        <v>6171564</v>
-      </c>
-      <c r="BC24" t="n">
-        <v>6171564</v>
-      </c>
-      <c r="BD24" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE24" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF24" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG24" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH24" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI24" t="n">
-        <v>0</v>
-      </c>
-      <c r="BJ24" t="n">
-        <v>0</v>
-      </c>
-      <c r="BK24" t="n">
-        <v>0</v>
-      </c>
-      <c r="BL24" t="n">
-        <v>0</v>
-      </c>
-      <c r="BM24" t="n">
-        <v>0</v>
-      </c>
-      <c r="BN24" t="n">
-        <v>0</v>
-      </c>
-      <c r="BO24" t="n">
-        <v>3273287</v>
-      </c>
-      <c r="BP24" t="n">
-        <v>1</v>
       </c>
       <c r="BQ24" t="n">
         <v>0</v>
@@ -6177,16 +6173,16 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>WCIL</t>
+          <t>TAINWALCHM</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>WESTERN CARRIERS (INDIA) LIMITED</t>
+          <t>TAINWALA CHEMICALS AND PLASTICS (INDIA) LIMITED</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -6194,10 +6190,10 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F25" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G25" t="n">
         <v>9</v>
@@ -6206,28 +6202,28 @@
         <v>-1</v>
       </c>
       <c r="I25" t="n">
-        <v>89.27</v>
+        <v>197.18</v>
       </c>
       <c r="J25" t="n">
-        <v>96.03</v>
+        <v>210.19</v>
       </c>
       <c r="K25" t="n">
-        <v>-7</v>
+        <v>-6.2</v>
       </c>
       <c r="L25" t="n">
-        <v>71.89</v>
+        <v>67.04000000000001</v>
       </c>
       <c r="M25" t="n">
-        <v>2.6</v>
+        <v>0.62</v>
       </c>
       <c r="N25" t="n">
-        <v>26023230</v>
+        <v>6171564</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
       </c>
       <c r="P25" t="n">
-        <v>26023230</v>
+        <v>6171564</v>
       </c>
       <c r="Q25" t="n">
         <v>0</v>
@@ -6241,94 +6237,94 @@
         <v>0</v>
       </c>
       <c r="T25" t="n">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="U25" t="inlineStr">
         <is>
-          <t>29-09-2026</t>
+          <t>28-09-2026</t>
         </is>
       </c>
       <c r="V25" t="n">
-        <v>0.286</v>
+        <v>0.334</v>
       </c>
       <c r="W25" t="n">
-        <v>910</v>
+        <v>185</v>
       </c>
       <c r="X25" t="n">
-        <v>24.8</v>
+        <v>23</v>
       </c>
       <c r="Y25" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="Z25" t="n">
-        <v>18.68</v>
+        <v>0.03</v>
       </c>
       <c r="AA25" t="n">
-        <v>-36</v>
+        <v>16</v>
       </c>
       <c r="AB25" t="n">
-        <v>0.85</v>
+        <v>0.03</v>
       </c>
       <c r="AC25" t="n">
-        <v>6.83</v>
+        <v>7.91</v>
       </c>
       <c r="AD25" t="n">
-        <v>0.26</v>
+        <v>0</v>
       </c>
       <c r="AE25" t="b">
         <v>0</v>
       </c>
       <c r="AF25" t="n">
-        <v>4.02</v>
+        <v>3.16</v>
       </c>
       <c r="AG25" t="n">
-        <v>88.95999999999999</v>
+        <v>208.99</v>
       </c>
       <c r="AH25" t="n">
-        <v>100.57</v>
+        <v>197.37</v>
       </c>
       <c r="AI25" t="n">
-        <v>10.2</v>
+        <v>10.4</v>
       </c>
       <c r="AJ25" t="n">
-        <v>96.02667896678967</v>
+        <v>210.188815475785</v>
       </c>
       <c r="AK25" t="n">
-        <v>-7</v>
+        <v>-6.2</v>
       </c>
       <c r="AL25" t="inlineStr">
         <is>
-          <t>Fresh</t>
+          <t>Active</t>
         </is>
       </c>
       <c r="AM25" t="inlineStr">
         <is>
-          <t>Early Accumulation</t>
+          <t>Confirmed Accumulation</t>
         </is>
       </c>
       <c r="AN25" t="inlineStr">
         <is>
-          <t>Early Accumulation</t>
+          <t>Confirmed Accumulation</t>
         </is>
       </c>
       <c r="AO25" t="inlineStr">
         <is>
-          <t>18-09-2026</t>
+          <t>18-08-2026</t>
         </is>
       </c>
       <c r="AP25" t="inlineStr">
         <is>
-          <t>29-09-2026</t>
+          <t>28-09-2026</t>
         </is>
       </c>
       <c r="AQ25" t="n">
-        <v>11</v>
+        <v>41</v>
       </c>
       <c r="AR25" t="n">
-        <v>18</v>
+        <v>49</v>
       </c>
       <c r="AS25" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AT25" t="n">
         <v>0</v>
@@ -6337,28 +6333,28 @@
         <v>2</v>
       </c>
       <c r="AV25" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="AW25" t="n">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="AX25" t="n">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="AY25" t="n">
         <v>0</v>
       </c>
       <c r="AZ25" t="n">
-        <v>16273230</v>
+        <v>226572</v>
       </c>
       <c r="BA25" t="n">
-        <v>26023230</v>
+        <v>3273287</v>
       </c>
       <c r="BB25" t="n">
-        <v>26023230</v>
+        <v>6171564</v>
       </c>
       <c r="BC25" t="n">
-        <v>26023230</v>
+        <v>6171564</v>
       </c>
       <c r="BD25" t="n">
         <v>0</v>
@@ -6394,7 +6390,7 @@
         <v>0</v>
       </c>
       <c r="BO25" t="n">
-        <v>26023230</v>
+        <v>3273287</v>
       </c>
       <c r="BP25" t="n">
         <v>1</v>
@@ -6409,12 +6405,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>SRGHFL</t>
+          <t>WCIL</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>SRG HOUSING FINANCE LIMITED</t>
+          <t>WESTERN CARRIERS (INDIA) LIMITED</t>
         </is>
       </c>
       <c r="C26" t="n">
@@ -6426,40 +6422,40 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="F26" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="G26" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="H26" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="I26" t="n">
-        <v>128.99</v>
+        <v>89.27</v>
       </c>
       <c r="J26" t="n">
-        <v>132.2</v>
+        <v>96.03</v>
       </c>
       <c r="K26" t="n">
-        <v>-2.4</v>
+        <v>-7</v>
       </c>
       <c r="L26" t="n">
-        <v>67.83</v>
+        <v>71.89</v>
       </c>
       <c r="M26" t="n">
-        <v>1.98</v>
+        <v>2.6</v>
       </c>
       <c r="N26" t="n">
-        <v>19830410</v>
+        <v>26023230</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
       </c>
       <c r="P26" t="n">
-        <v>19830410</v>
+        <v>26023230</v>
       </c>
       <c r="Q26" t="n">
         <v>0</v>
@@ -6477,92 +6473,96 @@
       </c>
       <c r="U26" t="inlineStr">
         <is>
-          <t>16-09-2026</t>
+          <t>29-09-2026</t>
         </is>
       </c>
       <c r="V26" t="n">
-        <v>0.977</v>
+        <v>0.29</v>
       </c>
       <c r="W26" t="n">
-        <v>203</v>
+        <v>896</v>
       </c>
       <c r="X26" t="n">
-        <v>5.93</v>
+        <v>24.4</v>
       </c>
       <c r="Y26" t="n">
-        <v>31</v>
-      </c>
-      <c r="Z26" t="inlineStr"/>
+        <v>9</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>18.68</v>
+      </c>
       <c r="AA26" t="n">
-        <v>35</v>
+        <v>-36</v>
       </c>
       <c r="AB26" t="n">
-        <v>5.39</v>
+        <v>0.85</v>
       </c>
       <c r="AC26" t="n">
-        <v>11.8</v>
+        <v>6.83</v>
       </c>
       <c r="AD26" t="n">
-        <v>2.89</v>
+        <v>0.26</v>
       </c>
       <c r="AE26" t="b">
         <v>0</v>
       </c>
-      <c r="AF26" t="inlineStr"/>
+      <c r="AF26" t="n">
+        <v>4.02</v>
+      </c>
       <c r="AG26" t="n">
-        <v>230.38</v>
+        <v>88.95999999999999</v>
       </c>
       <c r="AH26" t="n">
-        <v>266.47</v>
+        <v>100.57</v>
       </c>
       <c r="AI26" t="n">
-        <v>-48</v>
+        <v>10.2</v>
       </c>
       <c r="AJ26" t="n">
-        <v>132.2027333333333</v>
+        <v>96.02667896678967</v>
       </c>
       <c r="AK26" t="n">
-        <v>-2.4</v>
+        <v>-7</v>
       </c>
       <c r="AL26" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Fresh</t>
         </is>
       </c>
       <c r="AM26" t="inlineStr">
         <is>
-          <t>Confirmed Accumulation</t>
+          <t>Early Accumulation</t>
         </is>
       </c>
       <c r="AN26" t="inlineStr">
         <is>
-          <t>Confirmed Accumulation</t>
+          <t>Early Accumulation</t>
         </is>
       </c>
       <c r="AO26" t="inlineStr">
         <is>
-          <t>15-09-2026</t>
+          <t>18-09-2026</t>
         </is>
       </c>
       <c r="AP26" t="inlineStr">
         <is>
-          <t>16-09-2026</t>
+          <t>29-09-2026</t>
         </is>
       </c>
       <c r="AQ26" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="AR26" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="AS26" t="n">
-        <v>20</v>
+        <v>7</v>
       </c>
       <c r="AT26" t="n">
         <v>0</v>
       </c>
       <c r="AU26" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AV26" t="n">
         <v>3</v>
@@ -6577,16 +6577,16 @@
         <v>0</v>
       </c>
       <c r="AZ26" t="n">
-        <v>0</v>
+        <v>16273230</v>
       </c>
       <c r="BA26" t="n">
-        <v>19830410</v>
+        <v>26023230</v>
       </c>
       <c r="BB26" t="n">
-        <v>19830410</v>
+        <v>26023230</v>
       </c>
       <c r="BC26" t="n">
-        <v>19830410</v>
+        <v>26023230</v>
       </c>
       <c r="BD26" t="n">
         <v>0</v>
@@ -6622,10 +6622,10 @@
         <v>0</v>
       </c>
       <c r="BO26" t="n">
-        <v>19830410</v>
+        <v>26023230</v>
       </c>
       <c r="BP26" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BQ26" t="n">
         <v>0</v>
@@ -6709,10 +6709,10 @@
         </is>
       </c>
       <c r="V27" t="n">
-        <v>1.86</v>
+        <v>1.829</v>
       </c>
       <c r="W27" t="n">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="X27" t="inlineStr"/>
       <c r="Y27" t="n">
@@ -6939,13 +6939,13 @@
         </is>
       </c>
       <c r="V28" t="n">
-        <v>0.519</v>
+        <v>0.514</v>
       </c>
       <c r="W28" t="n">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="X28" t="n">
-        <v>35.9</v>
+        <v>36.3</v>
       </c>
       <c r="Y28" t="n">
         <v>-44</v>
@@ -7171,13 +7171,13 @@
         </is>
       </c>
       <c r="V29" t="n">
-        <v>0.134</v>
+        <v>0.136</v>
       </c>
       <c r="W29" t="n">
-        <v>596</v>
+        <v>589</v>
       </c>
       <c r="X29" t="n">
-        <v>13.1</v>
+        <v>13</v>
       </c>
       <c r="Y29" t="n">
         <v>-1</v>
@@ -7403,13 +7403,13 @@
         </is>
       </c>
       <c r="V30" t="n">
-        <v>0.044</v>
+        <v>0.043</v>
       </c>
       <c r="W30" t="n">
-        <v>1586</v>
+        <v>1602</v>
       </c>
       <c r="X30" t="n">
-        <v>20.7</v>
+        <v>20.9</v>
       </c>
       <c r="Y30" t="n">
         <v>10</v>
@@ -7635,13 +7635,13 @@
         </is>
       </c>
       <c r="V31" t="n">
-        <v>0.833</v>
+        <v>0.83</v>
       </c>
       <c r="W31" t="n">
-        <v>3793</v>
+        <v>3807</v>
       </c>
       <c r="X31" t="n">
-        <v>26.5</v>
+        <v>26.6</v>
       </c>
       <c r="Y31" t="n">
         <v>2</v>
@@ -7867,13 +7867,13 @@
         </is>
       </c>
       <c r="V32" t="n">
-        <v>0.233</v>
+        <v>0.241</v>
       </c>
       <c r="W32" t="n">
-        <v>278</v>
+        <v>268</v>
       </c>
       <c r="X32" t="n">
-        <v>14.7</v>
+        <v>14.1</v>
       </c>
       <c r="Y32" t="n">
         <v>16</v>
@@ -8099,13 +8099,13 @@
         </is>
       </c>
       <c r="V33" t="n">
-        <v>0.667</v>
+        <v>0.643</v>
       </c>
       <c r="W33" t="n">
-        <v>352</v>
+        <v>365</v>
       </c>
       <c r="X33" t="n">
-        <v>1137</v>
+        <v>1177</v>
       </c>
       <c r="Y33" t="n">
         <v>-61</v>
@@ -8327,13 +8327,13 @@
         </is>
       </c>
       <c r="V34" t="n">
-        <v>0.374</v>
+        <v>0.364</v>
       </c>
       <c r="W34" t="n">
-        <v>374</v>
+        <v>385</v>
       </c>
       <c r="X34" t="n">
-        <v>92.59999999999999</v>
+        <v>95.2</v>
       </c>
       <c r="Y34" t="n">
         <v>246</v>
@@ -8785,13 +8785,13 @@
         </is>
       </c>
       <c r="V36" t="n">
-        <v>0.233</v>
+        <v>0.226</v>
       </c>
       <c r="W36" t="n">
-        <v>1715</v>
+        <v>1766</v>
       </c>
       <c r="X36" t="n">
-        <v>18.1</v>
+        <v>18.7</v>
       </c>
       <c r="Y36" t="n">
         <v>-3</v>
@@ -9017,13 +9017,13 @@
         </is>
       </c>
       <c r="V37" t="n">
-        <v>0.042</v>
+        <v>0.041</v>
       </c>
       <c r="W37" t="n">
-        <v>3170</v>
+        <v>3246</v>
       </c>
       <c r="X37" t="n">
-        <v>18.8</v>
+        <v>19.2</v>
       </c>
       <c r="Y37" t="n">
         <v>-4</v>
@@ -9252,7 +9252,7 @@
         <v>0.011</v>
       </c>
       <c r="W38" t="n">
-        <v>4185</v>
+        <v>4173</v>
       </c>
       <c r="X38" t="inlineStr"/>
       <c r="Y38" t="n">
@@ -9482,10 +9482,10 @@
         <v>0</v>
       </c>
       <c r="W39" t="n">
-        <v>4986</v>
+        <v>5284</v>
       </c>
       <c r="X39" t="n">
-        <v>11.7</v>
+        <v>12.4</v>
       </c>
       <c r="Y39" t="n">
         <v>26</v>
@@ -9711,13 +9711,13 @@
         </is>
       </c>
       <c r="V40" t="n">
-        <v>0.109</v>
+        <v>0.11</v>
       </c>
       <c r="W40" t="n">
-        <v>456</v>
+        <v>451</v>
       </c>
       <c r="X40" t="n">
-        <v>7.37</v>
+        <v>7.29</v>
       </c>
       <c r="Y40" t="n">
         <v>118</v>
@@ -9942,7 +9942,7 @@
         <v>0.078</v>
       </c>
       <c r="W41" t="n">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="X41" t="n">
         <v>12.8</v>
@@ -10171,13 +10171,13 @@
         </is>
       </c>
       <c r="V42" t="n">
-        <v>0.125</v>
+        <v>0.131</v>
       </c>
       <c r="W42" t="n">
-        <v>162</v>
+        <v>154</v>
       </c>
       <c r="X42" t="n">
-        <v>37.4</v>
+        <v>35.5</v>
       </c>
       <c r="Y42" t="n">
         <v>19</v>
@@ -10406,7 +10406,7 @@
         <v>0.053</v>
       </c>
       <c r="W43" t="n">
-        <v>937</v>
+        <v>938</v>
       </c>
       <c r="X43" t="inlineStr"/>
       <c r="Y43" t="n">
@@ -10570,7 +10570,7 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -10578,7 +10578,7 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F44" t="n">
         <v>8</v>
@@ -10633,13 +10633,13 @@
         </is>
       </c>
       <c r="V44" t="n">
-        <v>0.107</v>
+        <v>0.099</v>
       </c>
       <c r="W44" t="n">
-        <v>239</v>
+        <v>258</v>
       </c>
       <c r="X44" t="n">
-        <v>25.6</v>
+        <v>27.6</v>
       </c>
       <c r="Y44" t="n">
         <v>24</v>
@@ -10868,7 +10868,7 @@
         <v>0.006</v>
       </c>
       <c r="W45" t="n">
-        <v>4858</v>
+        <v>4838</v>
       </c>
       <c r="X45" t="n">
         <v>12.5</v>
@@ -11096,10 +11096,10 @@
         <v>0</v>
       </c>
       <c r="W46" t="n">
-        <v>3825</v>
+        <v>3772</v>
       </c>
       <c r="X46" t="n">
-        <v>86.09999999999999</v>
+        <v>84.90000000000001</v>
       </c>
       <c r="Y46" t="n">
         <v>42</v>
@@ -11325,13 +11325,13 @@
         </is>
       </c>
       <c r="V47" t="n">
-        <v>0.217</v>
+        <v>0.22</v>
       </c>
       <c r="W47" t="n">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="X47" t="n">
-        <v>24.6</v>
+        <v>24.2</v>
       </c>
       <c r="Y47" t="n">
         <v>21</v>
@@ -11560,10 +11560,10 @@
         <v>0</v>
       </c>
       <c r="W48" t="n">
-        <v>111934</v>
+        <v>110231</v>
       </c>
       <c r="X48" t="n">
-        <v>32.2</v>
+        <v>31.8</v>
       </c>
       <c r="Y48" t="n">
         <v>18</v>
@@ -12559,105 +12559,105 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>TAINWALCHM</t>
+          <t>SRGHFL</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>TAINWALA CHEMICALS AND PLASTICS (INDIA) LIMITED</t>
+          <t>SRG HOUSING FINANCE LIMITED</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>197.18</v>
+        <v>128.99</v>
       </c>
       <c r="D24" t="n">
-        <v>210.19</v>
+        <v>132.2</v>
       </c>
       <c r="E24" t="n">
-        <v>-6.2</v>
+        <v>-2.4</v>
       </c>
       <c r="F24" t="n">
-        <v>67.04000000000001</v>
+        <v>67.83</v>
       </c>
       <c r="G24" t="n">
-        <v>0.62</v>
+        <v>1.98</v>
       </c>
       <c r="H24" t="n">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>28-09-2026</t>
+          <t>16-09-2026</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>WCIL</t>
+          <t>TAINWALCHM</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>WESTERN CARRIERS (INDIA) LIMITED</t>
+          <t>TAINWALA CHEMICALS AND PLASTICS (INDIA) LIMITED</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>89.27</v>
+        <v>197.18</v>
       </c>
       <c r="D25" t="n">
-        <v>96.03</v>
+        <v>210.19</v>
       </c>
       <c r="E25" t="n">
-        <v>-7</v>
+        <v>-6.2</v>
       </c>
       <c r="F25" t="n">
-        <v>71.89</v>
+        <v>67.04000000000001</v>
       </c>
       <c r="G25" t="n">
-        <v>2.6</v>
+        <v>0.62</v>
       </c>
       <c r="H25" t="n">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>29-09-2026</t>
+          <t>28-09-2026</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>SRGHFL</t>
+          <t>WCIL</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>SRG HOUSING FINANCE LIMITED</t>
+          <t>WESTERN CARRIERS (INDIA) LIMITED</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>128.99</v>
+        <v>89.27</v>
       </c>
       <c r="D26" t="n">
-        <v>132.2</v>
+        <v>96.03</v>
       </c>
       <c r="E26" t="n">
-        <v>-2.4</v>
+        <v>-7</v>
       </c>
       <c r="F26" t="n">
-        <v>67.83</v>
+        <v>71.89</v>
       </c>
       <c r="G26" t="n">
-        <v>1.98</v>
+        <v>2.6</v>
       </c>
       <c r="H26" t="n">
         <v>3</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>16-09-2026</t>
+          <t>29-09-2026</t>
         </is>
       </c>
     </row>
